--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
   <si>
     <t>Filename</t>
   </si>
@@ -808,700 +808,697 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9852,0.0010,0.0005,0.0046</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.9863,0.0003,0.0003,0.0074</t>
-  </si>
-  <si>
-    <t>0.0048,0.0027,0.0047,0.9943</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9750,0.0027,0.0055,0.0037</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0086,0.0006,0.0011,0.9950</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0000,0.0001</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
+    <t>0.9982,0.0021,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9938,0.0004,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.0012,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.7892,0.0046,0.1701,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9973,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2629,0.0010,0.7576,0.0008</t>
+  </si>
+  <si>
+    <t>0.7986,0.0003,0.2663,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0128,0.0000,0.9893,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0006</t>
+  </si>
+  <si>
+    <t>0.0056,0.9942,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9898,0.0017,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0034,0.9999,0.0239</t>
+  </si>
+  <si>
+    <t>0.0015,0.9742,0.1142,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1033,0.0562,0.5598,0.0039</t>
+  </si>
+  <si>
+    <t>0.6458,0.3820,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.9867,0.0732,0.0001</t>
+  </si>
+  <si>
+    <t>0.0080,0.0016,0.9784,0.0020</t>
+  </si>
+  <si>
+    <t>0.0050,0.0013,0.9920,0.0013</t>
+  </si>
+  <si>
+    <t>0.0505,0.0025,0.9356,0.0006</t>
+  </si>
+  <si>
+    <t>0.0115,0.0000,0.9871,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0349,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.0002,0.3842</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9990,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0119,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0107,0.0000,0.9892,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0012,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0023,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9816,0.0049,0.0053,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0085</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9901,0.8510,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0042,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0013,0.9969,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9871,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9979,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.9905,0.0001,0.0114,0.0000</t>
+  </si>
+  <si>
+    <t>0.0179,0.0034,0.9655,0.0058</t>
+  </si>
+  <si>
+    <t>0.0069,0.0002,0.9909,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.9847,0.9596,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.8681,0.9622,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7367,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9921,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0028,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0019,0.9988</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9648,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9890,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9877,0.9753,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3045,0.9865,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9899,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9155,0.8768,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9908,0.0083,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0021,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0002,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.0083,0.0014,0.9863,0.0009</t>
-  </si>
-  <si>
-    <t>0.9967,0.0000,0.0039,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9962,0.0007</t>
-  </si>
-  <si>
-    <t>0.9892,0.0003,0.0090,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9981,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2869,0.0014,0.6856,0.0020</t>
-  </si>
-  <si>
-    <t>0.9865,0.0001,0.0150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0000,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.0001,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0099,0.0000,0.9886,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0016</t>
-  </si>
-  <si>
-    <t>0.2190,0.8560,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9541,0.0062,0.0149,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0117</t>
-  </si>
-  <si>
-    <t>0.0021,0.8072,0.5017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1209,0.0483,0.5883,0.0029</t>
-  </si>
-  <si>
-    <t>0.0544,0.9342,0.0132,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.9923,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.0048,0.9778,0.0023</t>
-  </si>
-  <si>
-    <t>0.0049,0.0052,0.9898,0.0010</t>
-  </si>
-  <si>
-    <t>0.0326,0.0025,0.9563,0.0003</t>
-  </si>
-  <si>
-    <t>0.2079,0.0001,0.8342,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0661,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9933,0.0203,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9902,0.0012,0.0971</t>
-  </si>
-  <si>
-    <t>0.0002,0.9985,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0239,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0001,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0552,0.0000,0.9639,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.9942,0.0047,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0039</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0000,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.8062,0.0000,0.3552,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9970,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.9878,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9982,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7916,0.2603,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9841,0.0008,0.0083,0.0002</t>
+  </si>
+  <si>
+    <t>0.9924,0.0001,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.9428,0.0031,0.0153,0.0045</t>
+  </si>
+  <si>
+    <t>0.4380,0.0103,0.4359,0.0038</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9570,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.8392,0.1882,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9820,0.0151,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0012,0.0005</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9984,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.5418,0.9914,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0191,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9815,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.9966,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9712,0.0001,0.0465,0.0001</t>
-  </si>
-  <si>
-    <t>0.9811,0.0032,0.0058,0.0003</t>
-  </si>
-  <si>
-    <t>0.0069,0.0011,0.9875,0.0045</t>
-  </si>
-  <si>
-    <t>0.0001,0.9946,0.7661,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9608,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9852,0.0000</t>
-  </si>
-  <si>
-    <t>0.0588,0.0002,0.0021,0.9731</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
+    <t>0.9992,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9441,0.9111,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9598,0.3206,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.2888,0.0025,0.6735,0.0006</t>
+  </si>
+  <si>
+    <t>0.9674,0.0000,0.0654,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0162,0.0001,0.0007,0.9916</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9939,0.8459,0.0000</t>
+  </si>
+  <si>
+    <t>0.0142,0.9651,0.0086,0.0042</t>
+  </si>
+  <si>
+    <t>0.0265,0.9603,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0112,0.0000,0.0002,0.9956</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0078,0.9975,0.0165</t>
+  </si>
+  <si>
+    <t>0.9944,0.0000,0.0002,0.0079</t>
+  </si>
+  <si>
+    <t>0.9793,0.0010,0.0087,0.0011</t>
+  </si>
+  <si>
+    <t>0.2109,0.7523,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0012,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.3045,0.3487,0.0304,0.0021</t>
+  </si>
+  <si>
+    <t>0.9502,0.0150,0.0132,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0018,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7266,0.1164,0.0003,0.0042</t>
+  </si>
+  <si>
+    <t>0.9415,0.0879,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.4437,0.6528,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0163,0.0003,0.9841,0.0004</t>
+  </si>
+  <si>
+    <t>0.9931,0.0059,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8878,0.1441,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0233,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0096,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.1037,0.0004,0.9132,0.0003</t>
+  </si>
+  <si>
+    <t>0.0183,0.0010,0.9790,0.0005</t>
+  </si>
+  <si>
+    <t>0.0055,0.0003,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.1360,0.0308,0.6994,0.0008</t>
+  </si>
+  <si>
+    <t>0.0061,0.0466,0.9405,0.0012</t>
+  </si>
+  <si>
+    <t>0.1911,0.0059,0.8410,0.0005</t>
+  </si>
+  <si>
+    <t>0.3608,0.0022,0.5015,0.0031</t>
+  </si>
+  <si>
+    <t>0.2417,0.0009,0.7924,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9972,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0080,0.9917,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.5010,0.5896,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0217,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.6076,0.5035,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9929,0.0008,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.6257,0.0194,0.0181,0.0774</t>
+  </si>
+  <si>
+    <t>0.9618,0.0005,0.0408,0.0004</t>
+  </si>
+  <si>
+    <t>0.0201,0.0003,0.9789,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0226,0.0794,0.8807,0.0085</t>
+  </si>
+  <si>
+    <t>0.0131,0.0111,0.9741,0.0003</t>
+  </si>
+  <si>
+    <t>0.1623,0.0003,0.9097,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0012,0.9975,0.0011</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9888,0.0085,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9990,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0021,0.9992,0.0008</t>
+  </si>
+  <si>
+    <t>0.0102,0.0729,0.8911,0.0005</t>
+  </si>
+  <si>
+    <t>0.2408,0.0001,0.0359,0.4360</t>
+  </si>
+  <si>
+    <t>0.0031,0.0005,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9551,0.9593,0.0001</t>
+  </si>
+  <si>
+    <t>0.0211,0.0052,0.9717,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0025,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.0029,0.9910,0.0006</t>
+  </si>
+  <si>
+    <t>0.9978,0.0000,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.7437,0.0005,0.3873,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0003,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0022,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9911,0.0068,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0037,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0263,0.9843,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0029,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.0040,0.9869,0.0019</t>
+  </si>
+  <si>
+    <t>0.0069,0.0138,0.9722,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.1737,0.0000,0.8299,0.0008</t>
+  </si>
+  <si>
+    <t>0.0040,0.0005,0.9911,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0006,0.9940,0.0029</t>
+  </si>
+  <si>
+    <t>0.9888,0.0000,0.0008,0.0118</t>
+  </si>
+  <si>
+    <t>0.0077,0.0037,0.0000,0.9963</t>
+  </si>
+  <si>
+    <t>0.0023,0.0002,0.0029,0.9969</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0003,0.0008,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9869,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9120,0.9704,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9056,0.8270,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9967,0.3155,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9508,0.9762,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9945,0.0048,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0050,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9936,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.0072,0.9887,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7737,0.2505,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9803,0.0020,0.0055,0.0010</t>
-  </si>
-  <si>
-    <t>0.0612,0.0001,0.9533,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0012,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0572,0.0041,0.9177,0.0025</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9175,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9992,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.6410,0.3060,0.0139,0.0005</t>
-  </si>
-  <si>
-    <t>0.9304,0.0705,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9559,0.7984,0.0013</t>
-  </si>
-  <si>
-    <t>0.0019,0.1881,0.9478,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0107,0.9916,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9031,0.0014,0.0552,0.0019</t>
-  </si>
-  <si>
-    <t>0.7951,0.0000,0.3217,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0000,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.0255,0.0000,0.0000,0.9940</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9825,0.9579,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.9925,0.0013,0.0036</t>
-  </si>
-  <si>
-    <t>0.7304,0.3147,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2657,0.0001,0.0011,0.8576</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0076,0.9990,0.0035</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9333,0.0003,0.0522,0.0008</t>
-  </si>
-  <si>
-    <t>0.9262,0.0370,0.0072,0.0009</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0023,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.4771,0.2227,0.0246,0.0010</t>
-  </si>
-  <si>
-    <t>0.9911,0.0049,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0007,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0023,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8690,0.0610,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.4594,0.6864,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.6365,0.5498,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0055,0.0018,0.9940,0.0005</t>
-  </si>
-  <si>
-    <t>0.9928,0.0048,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9860,0.0158,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9968,0.0011,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0360,0.9889,0.0004</t>
-  </si>
-  <si>
-    <t>0.0311,0.0001,0.9670,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.2004,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0064,0.0007,0.9889,0.0005</t>
-  </si>
-  <si>
-    <t>0.2456,0.0125,0.6985,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0004,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0139,0.0323,0.9523,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.8417,0.2710,0.0013</t>
-  </si>
-  <si>
-    <t>0.0190,0.0094,0.9715,0.0006</t>
-  </si>
-  <si>
-    <t>0.0404,0.0141,0.7613,0.0282</t>
-  </si>
-  <si>
-    <t>0.0095,0.0004,0.9875,0.0004</t>
-  </si>
-  <si>
-    <t>0.0128,0.9878,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.9965,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8732,0.1709,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.7950,0.2324,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0547,0.9560,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9779,0.0047,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9729,0.0010,0.0110,0.0019</t>
-  </si>
-  <si>
-    <t>0.2469,0.0304,0.6581,0.0017</t>
-  </si>
-  <si>
-    <t>0.9784,0.0000,0.0253,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9974,0.0017</t>
-  </si>
-  <si>
-    <t>0.0737,0.1299,0.4047,0.0061</t>
-  </si>
-  <si>
-    <t>0.0040,0.0286,0.9847,0.0003</t>
-  </si>
-  <si>
-    <t>0.1304,0.0011,0.8909,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.0751,0.9715,0.0022</t>
-  </si>
-  <si>
-    <t>0.9951,0.0032,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0051,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0008</t>
-  </si>
-  <si>
-    <t>0.1571,0.3648,0.1320,0.0013</t>
-  </si>
-  <si>
-    <t>0.9948,0.0002,0.0012,0.0016</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0043,0.9982,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.3265,0.9860,0.0006</t>
-  </si>
-  <si>
-    <t>0.0055,0.0063,0.9827,0.0024</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0020,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0166,0.0029,0.9757,0.0005</t>
-  </si>
-  <si>
-    <t>0.9905,0.0000,0.0110,0.0002</t>
-  </si>
-  <si>
-    <t>0.8584,0.0002,0.2460,0.0002</t>
-  </si>
-  <si>
-    <t>0.9953,0.0001,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0026,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0067,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0008,0.9976,0.0004</t>
-  </si>
-  <si>
-    <t>0.0351,0.0119,0.9281,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0538,0.0002,0.8923,0.0098</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9982,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.0003,0.9958,0.0009</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0001,0.0023</t>
-  </si>
-  <si>
-    <t>0.0043,0.0009,0.0000,0.9984</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0039,0.9980</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.9076,0.0002,0.0001,0.0882</t>
+    <t>0.6588,0.0006,0.0004,0.4216</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1884,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1901,7 +1898,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1915,7 +1912,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1929,7 +1926,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1943,7 +1940,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1957,7 +1954,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1971,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1985,7 +1982,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1999,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2013,7 +2010,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2041,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2055,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,7 +2066,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2097,7 +2094,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2111,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2125,7 +2122,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2139,7 +2136,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2153,7 +2150,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2167,7 +2164,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2181,7 +2178,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,7 +2192,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2209,7 +2206,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2223,7 +2220,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2237,7 +2234,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2251,7 +2248,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,7 +2262,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2279,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,7 +2290,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,7 +2304,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2321,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,10 +2329,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2349,7 +2346,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2363,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2391,7 +2388,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2405,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2419,7 +2416,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2433,7 +2430,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,7 +2444,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2461,7 +2458,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2475,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2489,7 +2486,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2503,7 +2500,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2517,7 +2514,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2531,7 +2528,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2545,7 +2542,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2559,7 +2556,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2573,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2587,7 +2584,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2601,7 +2598,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2615,7 +2612,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2629,7 +2626,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2643,7 +2640,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2657,7 +2654,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2671,7 +2668,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2685,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2699,7 +2696,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2713,7 +2710,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2727,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2741,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2755,7 +2752,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2769,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2783,7 +2780,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2797,7 +2794,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2808,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2825,7 +2822,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2839,7 +2836,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,10 +2847,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2867,7 +2864,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2881,7 +2878,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,7 +2892,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2906,10 +2903,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2923,7 +2920,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2937,7 +2934,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2951,7 +2948,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2965,7 +2962,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2979,7 +2976,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2993,7 +2990,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3007,7 +3004,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3021,7 +3018,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3035,7 +3032,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3049,7 +3046,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,10 +3057,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,10 +3071,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3091,7 +3088,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3105,7 +3102,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3119,7 +3116,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3133,7 +3130,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3147,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3161,7 +3158,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3175,7 +3172,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3189,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3203,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3217,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3231,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3245,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>359</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3259,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3273,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3287,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3301,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3315,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3329,7 +3326,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3343,7 +3340,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3357,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,10 +3365,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3385,7 +3382,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3399,7 +3396,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3413,7 +3410,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3427,7 +3424,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3441,7 +3438,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3455,7 +3452,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3469,7 +3466,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,7 +3480,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,10 +3491,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,7 +3508,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3522,10 +3519,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3539,7 +3536,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3553,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>280</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3567,7 +3564,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3581,7 +3578,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3595,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3609,7 +3606,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3623,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3637,7 +3634,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3651,7 +3648,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>273</v>
+        <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3665,7 +3662,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3679,7 +3676,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3693,7 +3690,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3707,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3721,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3735,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3749,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,7 +3760,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,10 +3771,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3791,7 +3788,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3805,7 +3802,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3819,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,10 +3827,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3847,7 +3844,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3861,7 +3858,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,7 +3872,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3889,7 +3886,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3903,7 +3900,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3917,7 +3914,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3931,7 +3928,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3945,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3959,7 +3956,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3984,10 +3981,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4001,7 +3998,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4015,7 +4012,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4029,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4043,7 +4040,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4057,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4071,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,10 +4079,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4099,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4113,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4124,10 +4121,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4141,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4155,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4169,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4183,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4197,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4211,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4225,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>359</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4253,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4267,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>419</v>
+        <v>359</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4281,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,10 +4289,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4309,7 +4306,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4323,7 +4320,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4337,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4351,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4365,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>349</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4491,7 +4488,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>362</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4572,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>439</v>
@@ -4656,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
         <v>445</v>
@@ -4684,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
         <v>447</v>
@@ -4715,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>390</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4729,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4740,10 +4737,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,10 +4751,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4771,7 +4768,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,10 +4779,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4799,7 +4796,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4813,7 +4810,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4827,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4841,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4855,7 +4852,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4869,7 +4866,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4883,7 +4880,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4897,7 +4894,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4911,7 +4908,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4925,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4939,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>271</v>
+        <v>417</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4953,7 +4950,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4964,10 +4961,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,10 +4975,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4995,7 +4992,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5009,7 +5006,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,10 +5017,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5037,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>362</v>
+        <v>429</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5051,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5065,7 +5062,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5079,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5093,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5107,7 +5104,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5121,7 +5118,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5135,7 +5132,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5149,7 +5146,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5163,7 +5160,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5177,7 +5174,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>480</v>
+        <v>356</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5191,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5205,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5219,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5233,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>418</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5247,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>417</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5261,7 +5258,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5275,7 +5272,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,7 +5286,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5303,7 +5300,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5317,7 +5314,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,7 +5328,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5345,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5359,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,7 +5370,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5387,7 +5384,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5401,7 +5398,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5415,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>494</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5429,7 +5426,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>493</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5443,7 +5440,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
